--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -36,103 +36,103 @@
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
+    <t xml:space="preserve">Puerto Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puerto Montt</t>
   </si>
   <si>
-    <t xml:space="preserve">Puerto Varas</t>
+    <t xml:space="preserve">Puyehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
     <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chonchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Castro</t>
   </si>
   <si>
+    <t xml:space="preserve">Maullín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaitén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
-    <t xml:space="preserve">Chonchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puyehue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Juan de la Costa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quellón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pablo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fresia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cochamó</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Futaleufú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puerto Octay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Muermos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maullín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calbuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Negro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puqueldón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chaitén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llanquihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purranque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:46</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -559,13 +559,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10101</v>
+        <v>10109</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9762</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="3">
@@ -576,13 +576,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>10109</v>
+        <v>10202</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3949</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10105</v>
+        <v>10101</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1542</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="5">
@@ -610,13 +610,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10201</v>
+        <v>10304</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1267</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="6">
@@ -627,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>10301</v>
+        <v>10307</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1250</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7">
@@ -644,13 +644,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>10203</v>
+        <v>10105</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1172</v>
+        <v>884</v>
       </c>
     </row>
     <row r="8">
@@ -661,13 +661,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10304</v>
+        <v>10403</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1156</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9">
@@ -678,13 +678,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10403</v>
+        <v>10107</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>836</v>
+        <v>602</v>
       </c>
     </row>
     <row r="10">
@@ -695,13 +695,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>10306</v>
+        <v>10305</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>829</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11">
@@ -712,13 +712,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10205</v>
+        <v>10208</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>808</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12">
@@ -729,13 +729,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>10208</v>
+        <v>10203</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>741</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13">
@@ -746,13 +746,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10307</v>
+        <v>10205</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>626</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14">
@@ -763,13 +763,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>10202</v>
+        <v>10104</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>383</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15">
@@ -780,13 +780,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10104</v>
+        <v>10106</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>373</v>
+        <v>352</v>
       </c>
     </row>
     <row r="16">
@@ -797,7 +797,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10103</v>
+        <v>10102</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
@@ -814,13 +814,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10404</v>
+        <v>10201</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>343</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18">
@@ -831,13 +831,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>10402</v>
+        <v>10108</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>302</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19">
@@ -848,13 +848,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>10207</v>
+        <v>10302</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>225</v>
+        <v>254</v>
       </c>
     </row>
     <row r="20">
@@ -865,13 +865,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>10302</v>
+        <v>10404</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>225</v>
+        <v>252</v>
       </c>
     </row>
     <row r="21">
@@ -882,13 +882,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10106</v>
+        <v>10306</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>201</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22">
@@ -905,7 +905,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23">
@@ -916,13 +916,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>10108</v>
+        <v>10207</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
@@ -933,13 +933,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>10102</v>
+        <v>10303</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
@@ -950,13 +950,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10305</v>
+        <v>10206</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26">
@@ -967,13 +967,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10206</v>
+        <v>10210</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27">
@@ -990,7 +990,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28">
@@ -1007,7 +1007,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="29">
@@ -1018,13 +1018,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>10107</v>
+        <v>10103</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-41</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="30">
@@ -1035,13 +1035,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10210</v>
+        <v>10402</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-83</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="31">
@@ -1052,13 +1052,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>10303</v>
+        <v>10301</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-322</v>
+        <v>-28</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_los lagos.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:19</t>
+    <t xml:space="preserve">2026-10-05 07:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
